--- a/data/gravel/8Bar Mitte V3 2in1 2025.xlsx
+++ b/data/gravel/8Bar Mitte V3 2in1 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06494323-6453-EA4F-90CC-C1D6DC616E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F25A67-1272-2544-B71A-DF8E18645AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3400" yWindow="740" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,9 +371,6 @@
     <t>IS52/40</t>
   </si>
   <si>
-    <t>Mitte V3 2in1</t>
-  </si>
-  <si>
     <t>GRAVEL</t>
   </si>
   <si>
@@ -402,6 +399,9 @@
   </si>
   <si>
     <t>flip</t>
+  </si>
+  <si>
+    <t>Mitte V3 2in1 (gravel)</t>
   </si>
 </sst>
 </file>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -829,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -838,10 +838,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>88</v>
@@ -853,7 +853,7 @@
         <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="5">
         <v>525</v>
@@ -1159,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" s="5">
         <v>740</v>
@@ -1454,7 +1454,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1537,7 +1537,7 @@
         <v>78</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1545,7 +1545,7 @@
         <v>79</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
